--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92573861186</v>
+        <v>46157.93115253867</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93115253867</v>
+        <v>46157.93181707537</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93181707537</v>
+        <v>46157.93405151613</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93405151613</v>
+        <v>46157.93723221325</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93723221325</v>
+        <v>46158.28221053935</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221053935</v>
+        <v>46158.29700879904</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29700879904</v>
+        <v>46158.29820727793</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29820727793</v>
+        <v>46158.3339207792</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3339207792</v>
+        <v>46158.36861858226</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Кореньков- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36861858226</v>
+        <v>46158.37292508916</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
